--- a/data/trans_orig/IMC_inf_MED_R3-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R3-Provincia-trans_orig.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2012 (tasa de respuesta: 83,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -729,67 +729,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>14247</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>9592</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>21461</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.2654524715910742</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.1787113984880463</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.3998608549436372</v>
+      </c>
+      <c r="J4" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="D4" s="5" t="n">
-        <v>10125</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>6128</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>15142</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>0.2819390109274167</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>0.1706312617059764</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>0.4216272338941706</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="K4" s="5" t="n">
-        <v>6976</v>
+        <v>9073</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>3362</v>
+        <v>5404</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>11084</v>
+        <v>14037</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.2192529533364676</v>
+        <v>0.1975177763935075</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.105665315260016</v>
+        <v>0.1176405367163436</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.348363049312045</v>
+        <v>0.3055622336187083</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>17101</v>
+        <v>23321</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>12068</v>
+        <v>16631</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>23195</v>
+        <v>30233</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.2524908595826965</v>
+        <v>0.2341226701697428</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.1781792547232384</v>
+        <v>0.1669615665092532</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.3424624404288705</v>
+        <v>0.3035177667425268</v>
       </c>
     </row>
     <row r="5">
@@ -800,67 +800,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>25788</v>
+        <v>39425</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>20771</v>
+        <v>32211</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>29785</v>
+        <v>44080</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.7180609890725832</v>
+        <v>0.7345475284089258</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.5783727661058295</v>
+        <v>0.6001391450563626</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.8293687382940237</v>
+        <v>0.8212886015119537</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>24842</v>
+        <v>36864</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>20734</v>
+        <v>31900</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>28456</v>
+        <v>40533</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.7807470466635323</v>
+        <v>0.8024822236064925</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.6516369506879551</v>
+        <v>0.6944377663812918</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.8943346847399839</v>
+        <v>0.8823594632836571</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>50630</v>
+        <v>76288</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>44536</v>
+        <v>69376</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>55663</v>
+        <v>82978</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.7475091404173034</v>
+        <v>0.7658773298302571</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.6575375595711295</v>
+        <v>0.6964822332574733</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.8218207452767616</v>
+        <v>0.8330384334907468</v>
       </c>
     </row>
     <row r="6">
@@ -871,16 +871,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>35913</v>
+        <v>53672</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>35913</v>
+        <v>53672</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>35913</v>
+        <v>53672</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -892,16 +892,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>31818</v>
+        <v>45937</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>31818</v>
+        <v>45937</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>31818</v>
+        <v>45937</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -913,16 +913,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>67731</v>
+        <v>99609</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>67731</v>
+        <v>99609</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>67731</v>
+        <v>99609</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -946,67 +946,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>24758</v>
+        <v>27168</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>18617</v>
+        <v>20386</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>31647</v>
+        <v>35386</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.3046189662442481</v>
+        <v>0.2852516046945102</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.2290617217468384</v>
+        <v>0.214040134472884</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.3893856052088294</v>
+        <v>0.3715321253373796</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>19807</v>
+        <v>23743</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>14119</v>
+        <v>17620</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>26066</v>
+        <v>31478</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2673855778805653</v>
+        <v>0.2742613939035197</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.1906047583900343</v>
+        <v>0.2035406460106678</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3518781957811756</v>
+        <v>0.3636213340789082</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>44565</v>
+        <v>50911</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>35767</v>
+        <v>41433</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>54704</v>
+        <v>61585</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.2868650431884341</v>
+        <v>0.2800186534508048</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.2302309705778138</v>
+        <v>0.2278863389685884</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.3521338498338696</v>
+        <v>0.338726602244893</v>
       </c>
     </row>
     <row r="8">
@@ -1017,67 +1017,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>56517</v>
+        <v>68075</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>49628</v>
+        <v>59857</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>62658</v>
+        <v>74857</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.6953810337557519</v>
+        <v>0.7147483953054898</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.6106143947911702</v>
+        <v>0.6284678746626209</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.7709382782531605</v>
+        <v>0.7859598655271161</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>54269</v>
+        <v>62826</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>48010</v>
+        <v>55091</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>59957</v>
+        <v>68949</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.7326144221194347</v>
+        <v>0.7257386060964803</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.6481218042188243</v>
+        <v>0.6363786659210918</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.8093952416099657</v>
+        <v>0.7964593539893322</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>110786</v>
+        <v>130902</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>100647</v>
+        <v>120228</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>119584</v>
+        <v>140380</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.7131349568115659</v>
+        <v>0.7199813465491952</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.6478661501661304</v>
+        <v>0.661273397755107</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.7697690294221861</v>
+        <v>0.7721136610314111</v>
       </c>
     </row>
     <row r="9">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>81275</v>
+        <v>95243</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>81275</v>
+        <v>95243</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>81275</v>
+        <v>95243</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>74076</v>
+        <v>86569</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>74076</v>
+        <v>86569</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>74076</v>
+        <v>86569</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -1130,16 +1130,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>230</v>
+        <v>266</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>155351</v>
+        <v>181813</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>155351</v>
+        <v>181813</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>155351</v>
+        <v>181813</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -1163,67 +1163,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>10367</v>
+        <v>11715</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>6162</v>
+        <v>7372</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>15303</v>
+        <v>16725</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.1970249320041655</v>
+        <v>0.1944981674788208</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.1171125368177026</v>
+        <v>0.12239147884319</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.2908438476173356</v>
+        <v>0.2776730591252275</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>9558</v>
+        <v>10233</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>5739</v>
+        <v>6281</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>15314</v>
+        <v>16432</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.187800179339365</v>
+        <v>0.1745401114735619</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.1127702602953406</v>
+        <v>0.1071407466353957</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3008937765963516</v>
+        <v>0.2802867286526048</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>19925</v>
+        <v>21948</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>13915</v>
+        <v>15912</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>26634</v>
+        <v>30354</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.1924893234993134</v>
+        <v>0.1846540567363829</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.1344344612505783</v>
+        <v>0.133875852440719</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.257312524439906</v>
+        <v>0.2553795912885298</v>
       </c>
     </row>
     <row r="11">
@@ -1234,67 +1234,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>42249</v>
+        <v>48518</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>37313</v>
+        <v>43508</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>46454</v>
+        <v>52861</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.8029750679958345</v>
+        <v>0.8055018325211792</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.7091561523826644</v>
+        <v>0.7223269408747726</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.8828874631822975</v>
+        <v>0.8776085211568102</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>41336</v>
+        <v>48393</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>35580</v>
+        <v>42194</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>45155</v>
+        <v>52345</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.812199820660635</v>
+        <v>0.8254598885264381</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6991062234036484</v>
+        <v>0.719713271347395</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.8872297397046593</v>
+        <v>0.8928592533646043</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>83585</v>
+        <v>96912</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>76876</v>
+        <v>88506</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>89595</v>
+        <v>102948</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.8075106765006865</v>
+        <v>0.8153459432636171</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.7426874755600937</v>
+        <v>0.7446204087114702</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.8655655387494217</v>
+        <v>0.866124147559281</v>
       </c>
     </row>
     <row r="12">
@@ -1305,16 +1305,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>52616</v>
+        <v>60233</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>52616</v>
+        <v>60233</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>52616</v>
+        <v>60233</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -1326,16 +1326,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>50894</v>
+        <v>58626</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>50894</v>
+        <v>58626</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>50894</v>
+        <v>58626</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -1347,16 +1347,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>103510</v>
+        <v>118860</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>103510</v>
+        <v>118860</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>103510</v>
+        <v>118860</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -1380,67 +1380,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>16061</v>
+        <v>17807</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>10767</v>
+        <v>12109</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>22308</v>
+        <v>24691</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2855564316789023</v>
+        <v>0.2568890864579249</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.1914258942231699</v>
+        <v>0.1746841223840148</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3966328606683293</v>
+        <v>0.3561969443567023</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>7270</v>
+        <v>7939</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>3762</v>
+        <v>4381</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>12750</v>
+        <v>13733</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1410917888378873</v>
+        <v>0.128179817091444</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.07301137738971153</v>
+        <v>0.07073002932583895</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.2474488178861273</v>
+        <v>0.2217340665407515</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>23331</v>
+        <v>25746</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>15867</v>
+        <v>18511</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>30882</v>
+        <v>34354</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2164870635828831</v>
+        <v>0.1961538736912365</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.1472307619108143</v>
+        <v>0.1410371855690013</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.2865604235580514</v>
+        <v>0.2617390514660163</v>
       </c>
     </row>
     <row r="14">
@@ -1451,67 +1451,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>40183</v>
+        <v>51510</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>33936</v>
+        <v>44626</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>45477</v>
+        <v>57208</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7144435683210977</v>
+        <v>0.743110913542075</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.6033671393316694</v>
+        <v>0.6438030556432977</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.8085741057768296</v>
+        <v>0.8253158776159851</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>44255</v>
+        <v>53996</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>38775</v>
+        <v>48202</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>47763</v>
+        <v>57554</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.8589082111621127</v>
+        <v>0.871820182908556</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7525511821138728</v>
+        <v>0.7782659334592485</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.9269886226102885</v>
+        <v>0.9292699706741611</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>84438</v>
+        <v>105506</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>76887</v>
+        <v>96898</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>91902</v>
+        <v>112741</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7835129364171168</v>
+        <v>0.8038461263087635</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.7134395764419486</v>
+        <v>0.7382609485339838</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.8527692380891857</v>
+        <v>0.8589628144309989</v>
       </c>
     </row>
     <row r="15">
@@ -1522,16 +1522,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>56244</v>
+        <v>69317</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>56244</v>
+        <v>69317</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>56244</v>
+        <v>69317</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -1543,16 +1543,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>51525</v>
+        <v>61935</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>51525</v>
+        <v>61935</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>51525</v>
+        <v>61935</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -1564,16 +1564,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>107769</v>
+        <v>131252</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>107769</v>
+        <v>131252</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>107769</v>
+        <v>131252</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -1603,61 +1603,61 @@
         <v>7953</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>4327</v>
+        <v>4304</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>12190</v>
+        <v>12909</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.2647090735305641</v>
+        <v>0.2022406649355196</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.1440145712634134</v>
+        <v>0.1094423998120797</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.4057635635207453</v>
+        <v>0.328272253556563</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>4672</v>
+        <v>7256</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1706</v>
+        <v>3464</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>8649</v>
+        <v>12134</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.1747281168605573</v>
+        <v>0.1791846274709722</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.0638009147372163</v>
+        <v>0.08553423759038914</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.3234637675997309</v>
+        <v>0.2996370721040563</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>12625</v>
+        <v>15209</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>7580</v>
+        <v>9466</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>17843</v>
+        <v>21694</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.2223358795054674</v>
+        <v>0.1905431136958579</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.1334873112633509</v>
+        <v>0.1185872171321361</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.3142250994720736</v>
+        <v>0.2717899510079229</v>
       </c>
     </row>
     <row r="17">
@@ -1668,67 +1668,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>22090</v>
+        <v>31370</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>17853</v>
+        <v>26414</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>25716</v>
+        <v>35019</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.7352909264694358</v>
+        <v>0.7977593350644805</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.5942364364792552</v>
+        <v>0.6717277464434346</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.8559854287365868</v>
+        <v>0.89055760018792</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>22068</v>
+        <v>33241</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>18091</v>
+        <v>28363</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>25034</v>
+        <v>37033</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.8252718831394428</v>
+        <v>0.8208153725290278</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.6765362324002692</v>
+        <v>0.7003629278959438</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.9361990852627837</v>
+        <v>0.9144657624096109</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>44158</v>
+        <v>64611</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>38940</v>
+        <v>58126</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>49203</v>
+        <v>70354</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.7776641204945326</v>
+        <v>0.8094568863041421</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.6857749005279264</v>
+        <v>0.7282100489920772</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.8665126887366492</v>
+        <v>0.881412782867864</v>
       </c>
     </row>
     <row r="18">
@@ -1739,16 +1739,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>30043</v>
+        <v>39323</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>30043</v>
+        <v>39323</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>30043</v>
+        <v>39323</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -1760,16 +1760,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>26740</v>
+        <v>40497</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>26740</v>
+        <v>40497</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>26740</v>
+        <v>40497</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -1781,16 +1781,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>56783</v>
+        <v>79820</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>56783</v>
+        <v>79820</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>56783</v>
+        <v>79820</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -1814,67 +1814,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>8201</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>4442</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>13495</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.1681573859198577</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.09107550280826769</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.2767163855242713</v>
+      </c>
+      <c r="J19" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>7073</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>3796</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>11950</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>0.169734904434926</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>0.09109247468297446</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>0.2867636135633929</v>
-      </c>
-      <c r="J19" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="K19" s="5" t="n">
-        <v>5744</v>
+        <v>6969</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>3041</v>
+        <v>3637</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>10140</v>
+        <v>12732</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1303812354656226</v>
+        <v>0.1490075922940573</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.0690251849058644</v>
+        <v>0.07775704891677707</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.2301754192080569</v>
+        <v>0.2722298692250062</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>12817</v>
+        <v>15170</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>8568</v>
+        <v>9396</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>19288</v>
+        <v>21846</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.1495110764821942</v>
+        <v>0.1587827649650006</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.09994592586986847</v>
+        <v>0.09835036055747834</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.2249946184100857</v>
+        <v>0.2286646404462042</v>
       </c>
     </row>
     <row r="20">
@@ -1885,67 +1885,67 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>34599</v>
+        <v>40568</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>29722</v>
+        <v>35274</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>37876</v>
+        <v>44327</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.830265095565074</v>
+        <v>0.8318426140801423</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.7132363864366068</v>
+        <v>0.7232836144757288</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.9089075253170256</v>
+        <v>0.9089244971917324</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>38311</v>
+        <v>39802</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>33915</v>
+        <v>34039</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>41014</v>
+        <v>43134</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.8696187645343775</v>
+        <v>0.8509924077059426</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.7698245807919432</v>
+        <v>0.7277701307749938</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.9309748150941356</v>
+        <v>0.9222429510832226</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>72909</v>
+        <v>80369</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>66438</v>
+        <v>73693</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>77158</v>
+        <v>86143</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.8504889235178058</v>
+        <v>0.8412172350349995</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.7750053815899144</v>
+        <v>0.7713353595537955</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.9000540741301316</v>
+        <v>0.9016496394425215</v>
       </c>
     </row>
     <row r="21">
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>41672</v>
+        <v>48769</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>41672</v>
+        <v>48769</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>41672</v>
+        <v>48769</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -1977,16 +1977,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>44055</v>
+        <v>46771</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>44055</v>
+        <v>46771</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>44055</v>
+        <v>46771</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -1998,16 +1998,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>85726</v>
+        <v>95539</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>85726</v>
+        <v>95539</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>85726</v>
+        <v>95539</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -2037,61 +2037,61 @@
         <v>26426</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>19785</v>
+        <v>19462</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>34939</v>
+        <v>34297</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.2520515226137893</v>
+        <v>0.2244606850860137</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.1887084033229975</v>
+        <v>0.1653123083683194</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.3332509273889395</v>
+        <v>0.2913174969590346</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>16665</v>
+        <v>19023</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>10953</v>
+        <v>13149</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>24058</v>
+        <v>26371</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1600709256683901</v>
+        <v>0.1664908864271637</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.1052049054538536</v>
+        <v>0.1150833448559026</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2310774710076076</v>
+        <v>0.2308068456182186</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>43091</v>
+        <v>45448</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>34242</v>
+        <v>36386</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>53358</v>
+        <v>56286</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.2062216865557513</v>
+        <v>0.19590977466719</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.1638712453620685</v>
+        <v>0.1568450441758293</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.2553571989948036</v>
+        <v>0.2426251337621846</v>
       </c>
     </row>
     <row r="23">
@@ -2102,67 +2102,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>78416</v>
+        <v>91304</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>69903</v>
+        <v>83433</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>85057</v>
+        <v>98268</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.7479484773862107</v>
+        <v>0.7755393149139863</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.6667490726110605</v>
+        <v>0.7086825030409654</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.8112915966770026</v>
+        <v>0.8346876916316806</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>87448</v>
+        <v>95233</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>80055</v>
+        <v>87885</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>93160</v>
+        <v>101107</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.8399290743316099</v>
+        <v>0.8335091135728363</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.7689225289923923</v>
+        <v>0.7691931543817813</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.8947950945461464</v>
+        <v>0.8849166551440973</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>165864</v>
+        <v>186538</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>155597</v>
+        <v>175700</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>174713</v>
+        <v>195600</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.7937783134442487</v>
+        <v>0.80409022533281</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.7446428010051964</v>
+        <v>0.7573748662378154</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.8361287546379317</v>
+        <v>0.8431549558241707</v>
       </c>
     </row>
     <row r="24">
@@ -2173,16 +2173,16 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>104842</v>
+        <v>117730</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>104842</v>
+        <v>117730</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>104842</v>
+        <v>117730</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>1</v>
@@ -2194,16 +2194,16 @@
         <v>1</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>104113</v>
+        <v>114256</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>104113</v>
+        <v>114256</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>104113</v>
+        <v>114256</v>
       </c>
       <c r="N24" s="6" t="n">
         <v>1</v>
@@ -2215,16 +2215,16 @@
         <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>208955</v>
+        <v>231986</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>208955</v>
+        <v>231986</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>208955</v>
+        <v>231986</v>
       </c>
       <c r="U24" s="6" t="n">
         <v>1</v>
@@ -2248,67 +2248,67 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>44117</v>
+        <v>48266</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>36093</v>
+        <v>40412</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>52566</v>
+        <v>57813</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.3657297428628707</v>
+        <v>0.3409128218265909</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.2992052729598035</v>
+        <v>0.2854356544658162</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.4357656331722011</v>
+        <v>0.4083459155977427</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>38515</v>
+        <v>41100</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>30072</v>
+        <v>33383</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>46871</v>
+        <v>50499</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.32792523079734</v>
+        <v>0.2902635608199216</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.2560417494644416</v>
+        <v>0.2357633942887888</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3990714038891077</v>
+        <v>0.3566401161053993</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>82632</v>
+        <v>89366</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>71263</v>
+        <v>77157</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>94226</v>
+        <v>102250</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.3470798426025192</v>
+        <v>0.3155866771496097</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.2993283487211726</v>
+        <v>0.272470647186592</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.3957762332035195</v>
+        <v>0.3610831194824085</v>
       </c>
     </row>
     <row r="26">
@@ -2319,67 +2319,67 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>76511</v>
+        <v>93313</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>68062</v>
+        <v>83766</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>84535</v>
+        <v>101167</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.6342702571371294</v>
+        <v>0.6590871781734091</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.564234366827799</v>
+        <v>0.5916540844022572</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.7007947270401965</v>
+        <v>0.7145643455341829</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>78935</v>
+        <v>100496</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>70579</v>
+        <v>91097</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>87378</v>
+        <v>108213</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.6720747692026601</v>
+        <v>0.7097364391800784</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6009285961108924</v>
+        <v>0.6433598838946006</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.7439582505355584</v>
+        <v>0.764236605711211</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>229</v>
+        <v>288</v>
       </c>
       <c r="R26" s="5" t="n">
-        <v>155446</v>
+        <v>193809</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>143852</v>
+        <v>180925</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>166815</v>
+        <v>206018</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.6529201573974808</v>
+        <v>0.6844133228503902</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.6042237667964805</v>
+        <v>0.6389168805175915</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.7006716512788272</v>
+        <v>0.727529352813408</v>
       </c>
     </row>
     <row r="27">
@@ -2390,16 +2390,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>120628</v>
+        <v>141579</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>120628</v>
+        <v>141579</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>120628</v>
+        <v>141579</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -2411,16 +2411,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>117450</v>
+        <v>141596</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>117450</v>
+        <v>141596</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>117450</v>
+        <v>141596</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -2432,16 +2432,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>351</v>
+        <v>420</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>238078</v>
+        <v>283175</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>238078</v>
+        <v>283175</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>238078</v>
+        <v>283175</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -2465,67 +2465,67 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>146880</v>
+        <v>161783</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>131211</v>
+        <v>144506</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>164370</v>
+        <v>180688</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.2807150773981362</v>
+        <v>0.2584946618186473</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.2507700043450333</v>
+        <v>0.2308892092994714</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.3141416914663673</v>
+        <v>0.2887002357744994</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>109207</v>
+        <v>125336</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>94636</v>
+        <v>109860</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>124532</v>
+        <v>142704</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.218121588944378</v>
+        <v>0.2102289689071407</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.1890184602461841</v>
+        <v>0.1842705667851912</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2487304796293391</v>
+        <v>0.2393603117884866</v>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="R28" s="5" t="n">
-        <v>256087</v>
+        <v>287119</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>234026</v>
+        <v>261844</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>279500</v>
+        <v>312103</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.2501080246998801</v>
+        <v>0.2349478947396191</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.2285624377737537</v>
+        <v>0.214265771825843</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.2729750716981049</v>
+        <v>0.2553922250896048</v>
       </c>
     </row>
     <row r="29">
@@ -2536,67 +2536,67 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>544</v>
+        <v>669</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>376354</v>
+        <v>464083</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>358864</v>
+        <v>445178</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>392023</v>
+        <v>481360</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.7192849226018638</v>
+        <v>0.7415053381813527</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.6858583085336327</v>
+        <v>0.7112997642255007</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.7492299956549663</v>
+        <v>0.7691107907005286</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>560</v>
+        <v>675</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>391463</v>
+        <v>470852</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>376138</v>
+        <v>453484</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>406034</v>
+        <v>486328</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.7818784110556219</v>
+        <v>0.7897710310928593</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.751269520370661</v>
+        <v>0.7606396882115134</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.8109815397538159</v>
+        <v>0.8157294332148085</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>1104</v>
+        <v>1344</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>767817</v>
+        <v>934935</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>744404</v>
+        <v>909951</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>789878</v>
+        <v>960210</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.74989197530012</v>
+        <v>0.7650521052603809</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.7270249283018951</v>
+        <v>0.7446077749103951</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.7714375622262463</v>
+        <v>0.7857342281741569</v>
       </c>
     </row>
     <row r="30">
@@ -2607,16 +2607,16 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>752</v>
+        <v>896</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>1</v>
@@ -2628,16 +2628,16 @@
         <v>1</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>718</v>
+        <v>854</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="N30" s="6" t="n">
         <v>1</v>
@@ -2649,16 +2649,16 @@
         <v>1</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>1470</v>
+        <v>1750</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="U30" s="6" t="n">
         <v>1</v>
@@ -2734,7 +2734,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2016 (tasa de respuesta: 82,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2918,67 +2918,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>13343</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>8491</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>18686</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.2503126008165801</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.1592943672843305</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.3505496511644096</v>
+      </c>
+      <c r="J4" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D4" s="5" t="n">
-        <v>8304</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>5004</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>12069</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>0.2892254254887906</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>0.1742725774689705</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>0.4203538803132207</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="K4" s="5" t="n">
-        <v>7156</v>
+        <v>8118</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>3781</v>
+        <v>4419</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>11545</v>
+        <v>12914</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.2411179909226401</v>
+        <v>0.1667498381256748</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.127388745953418</v>
+        <v>0.09077088648635916</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3890039866318502</v>
+        <v>0.2652460461084846</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>15460</v>
+        <v>21461</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>10205</v>
+        <v>15329</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>21002</v>
+        <v>28815</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.264773299366759</v>
+        <v>0.2104235450199991</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.1747673574856408</v>
+        <v>0.1502972685818266</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.3596788934354394</v>
+        <v>0.2825289425903295</v>
       </c>
     </row>
     <row r="5">
@@ -2989,67 +2989,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>20407</v>
+        <v>39961</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>16642</v>
+        <v>34618</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>23707</v>
+        <v>44813</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.7107745745112094</v>
+        <v>0.7496873991834199</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.5796461196867794</v>
+        <v>0.6494503488355903</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.8257274225310294</v>
+        <v>0.8407056327156691</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>22522</v>
+        <v>40567</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>18133</v>
+        <v>35771</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>25897</v>
+        <v>44266</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.7588820090773599</v>
+        <v>0.8332501618743252</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.6109960133681497</v>
+        <v>0.7347539538915153</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.872611254046582</v>
+        <v>0.9092291135136409</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>42930</v>
+        <v>80528</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>37388</v>
+        <v>73174</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>48185</v>
+        <v>86660</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.735226700633241</v>
+        <v>0.789576454980001</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.6403211065645606</v>
+        <v>0.7174710574096705</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.8252326425143592</v>
+        <v>0.8497027314181734</v>
       </c>
     </row>
     <row r="6">
@@ -3060,16 +3060,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>28711</v>
+        <v>53304</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>28711</v>
+        <v>53304</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>28711</v>
+        <v>53304</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -3081,16 +3081,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>29678</v>
+        <v>48685</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>29678</v>
+        <v>48685</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>29678</v>
+        <v>48685</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -3102,16 +3102,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>58390</v>
+        <v>101989</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>58390</v>
+        <v>101989</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>58390</v>
+        <v>101989</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -3135,67 +3135,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>23588</v>
+        <v>26917</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>17200</v>
+        <v>19276</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>30703</v>
+        <v>34828</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.2974474138136327</v>
+        <v>0.2719524861913415</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.2168931153297844</v>
+        <v>0.1947535001322798</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.3871594996767837</v>
+        <v>0.3518714546356553</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>13618</v>
+        <v>14219</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>8648</v>
+        <v>8896</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>19864</v>
+        <v>20106</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.1760906830165831</v>
+        <v>0.1600511635163882</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.1118232230109585</v>
+        <v>0.1001402551126636</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2568509048451824</v>
+        <v>0.2263231994049044</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>37206</v>
+        <v>41136</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>29392</v>
+        <v>32781</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>47170</v>
+        <v>51195</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.2375310080122792</v>
+        <v>0.2190223720583206</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.1876455185763573</v>
+        <v>0.1745367328755554</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.3011415484237331</v>
+        <v>0.2725825682429706</v>
       </c>
     </row>
     <row r="8">
@@ -3206,67 +3206,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>55714</v>
+        <v>72061</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>48599</v>
+        <v>64150</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>62102</v>
+        <v>79702</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.7025525861863673</v>
+        <v>0.7280475138086585</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.6128405003232162</v>
+        <v>0.6481285453643446</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.7831068846702152</v>
+        <v>0.8052464998677201</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>63717</v>
+        <v>74619</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>57471</v>
+        <v>68732</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>68687</v>
+        <v>79942</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.8239093169834169</v>
+        <v>0.8399488364836118</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.7431490951548172</v>
+        <v>0.7736768005950956</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.8881767769890415</v>
+        <v>0.8998597448873366</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>119431</v>
+        <v>146680</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>109467</v>
+        <v>136621</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>127245</v>
+        <v>155035</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.7624689919877208</v>
+        <v>0.7809776279416794</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.6988584515762668</v>
+        <v>0.7274174317570294</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.8123544814236427</v>
+        <v>0.8254632671244446</v>
       </c>
     </row>
     <row r="9">
@@ -3277,16 +3277,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>79302</v>
+        <v>98978</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>79302</v>
+        <v>98978</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>79302</v>
+        <v>98978</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -3298,16 +3298,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>77335</v>
+        <v>88838</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>77335</v>
+        <v>88838</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>77335</v>
+        <v>88838</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -3319,16 +3319,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>228</v>
+        <v>275</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>156637</v>
+        <v>187816</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>156637</v>
+        <v>187816</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>156637</v>
+        <v>187816</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -3358,19 +3358,19 @@
         <v>12875</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>8094</v>
+        <v>7966</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>18974</v>
+        <v>18305</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.2185986703454311</v>
+        <v>0.2112310604131865</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.137431335382515</v>
+        <v>0.1306964605797341</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.3221431807315184</v>
+        <v>0.3003058420361637</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>7</v>
@@ -3379,40 +3379,40 @@
         <v>5212</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>2222</v>
+        <v>2277</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>9487</v>
+        <v>10412</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.09308456868747475</v>
+        <v>0.09183955964445942</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.03967327465946137</v>
+        <v>0.04012779706313417</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.169428306873737</v>
+        <v>0.1834607900823142</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>25</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>18088</v>
+        <v>18087</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>12230</v>
+        <v>12637</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>25529</v>
+        <v>25465</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.157426760354193</v>
+        <v>0.1536639661900095</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.1064409601792683</v>
+        <v>0.1073594004864074</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.2221952581489592</v>
+        <v>0.2163438162613572</v>
       </c>
     </row>
     <row r="11">
@@ -3423,67 +3423,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>46023</v>
+        <v>48078</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>39924</v>
+        <v>42648</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>50804</v>
+        <v>52987</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.7814013296545689</v>
+        <v>0.7887689395868135</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.6778568192684817</v>
+        <v>0.6996941579638365</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.8625686646174852</v>
+        <v>0.8693035394202659</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>50784</v>
+        <v>51543</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>46509</v>
+        <v>46343</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>53774</v>
+        <v>54478</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.9069154313125253</v>
+        <v>0.9081604403555406</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.8305716931262639</v>
+        <v>0.8165392099176864</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.9603267253405386</v>
+        <v>0.9598722029368659</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>96807</v>
+        <v>99621</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>89366</v>
+        <v>92243</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>102665</v>
+        <v>105071</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.842573239645807</v>
+        <v>0.8463360338099906</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.7778047418510408</v>
+        <v>0.7836561837386428</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.8935590398207317</v>
+        <v>0.8926405995135925</v>
       </c>
     </row>
     <row r="12">
@@ -3494,16 +3494,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>58898</v>
+        <v>60953</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>58898</v>
+        <v>60953</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>58898</v>
+        <v>60953</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -3515,16 +3515,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>55996</v>
+        <v>56755</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>55996</v>
+        <v>56755</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>55996</v>
+        <v>56755</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -3536,16 +3536,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>114895</v>
+        <v>117708</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>114895</v>
+        <v>117708</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>114895</v>
+        <v>117708</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -3569,67 +3569,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>12244</v>
+        <v>14841</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>7816</v>
+        <v>9862</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>18312</v>
+        <v>21758</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2799806255792562</v>
+        <v>0.2530517175208696</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.1787267406720276</v>
+        <v>0.1681564538375045</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.418740221942433</v>
+        <v>0.3709877337311537</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>5305</v>
+        <v>6062</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>2524</v>
+        <v>3007</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>9836</v>
+        <v>10705</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1534183601666187</v>
+        <v>0.1205696112964009</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.07300602698860841</v>
+        <v>0.05981586930725128</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.2844478327830304</v>
+        <v>0.2129295231298293</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>17549</v>
+        <v>20903</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>12462</v>
+        <v>14124</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>25114</v>
+        <v>28980</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2240952508427552</v>
+        <v>0.1919025173632026</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.1591408068395039</v>
+        <v>0.1296700472685627</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.3207056316469192</v>
+        <v>0.2660611931515268</v>
       </c>
     </row>
     <row r="14">
@@ -3640,67 +3640,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>31487</v>
+        <v>43808</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>25419</v>
+        <v>36891</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>35915</v>
+        <v>48787</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7200193744207438</v>
+        <v>0.7469482824791304</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.581259778057567</v>
+        <v>0.6290122662688465</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.8212732593279725</v>
+        <v>0.8318435461624953</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>29274</v>
+        <v>44214</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>24743</v>
+        <v>39571</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>32055</v>
+        <v>47269</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.8465816398333813</v>
+        <v>0.8794303887035991</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7155521672169705</v>
+        <v>0.7870704768701706</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.9269939730113916</v>
+        <v>0.9401841306927486</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>60761</v>
+        <v>88021</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>53196</v>
+        <v>79944</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>65848</v>
+        <v>94800</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7759047491572448</v>
+        <v>0.8080974826367974</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.679294368353081</v>
+        <v>0.7339388068484729</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.8408591931604962</v>
+        <v>0.8703299527314372</v>
       </c>
     </row>
     <row r="15">
@@ -3711,16 +3711,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>43731</v>
+        <v>58649</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>43731</v>
+        <v>58649</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>43731</v>
+        <v>58649</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -3732,16 +3732,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>34579</v>
+        <v>50276</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>34579</v>
+        <v>50276</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>34579</v>
+        <v>50276</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -3753,16 +3753,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>78310</v>
+        <v>108924</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>78310</v>
+        <v>108924</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>78310</v>
+        <v>108924</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -3786,25 +3786,25 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>4836</v>
+        <v>5436</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2150</v>
+        <v>2610</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>8995</v>
+        <v>9915</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.1378447068998319</v>
+        <v>0.1408079620049003</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.06128742166301877</v>
+        <v>0.06759777806010174</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.2563735173942316</v>
+        <v>0.2568345460534843</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>5</v>
@@ -3813,40 +3813,40 @@
         <v>3271</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1265</v>
+        <v>1224</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>6862</v>
+        <v>6760</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.1021625267236238</v>
+        <v>0.08661099703344929</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.03949511969915773</v>
+        <v>0.03241757657103625</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2143252002382691</v>
+        <v>0.1789819673856843</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>8108</v>
+        <v>8707</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>4493</v>
+        <v>4653</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>14088</v>
+        <v>13620</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.1208190380981204</v>
+        <v>0.1140064761994657</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.06695196453900393</v>
+        <v>0.06092439608079302</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.2099341350904598</v>
+        <v>0.1783317858425113</v>
       </c>
     </row>
     <row r="17">
@@ -3857,67 +3857,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>30250</v>
+        <v>33170</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>26091</v>
+        <v>28691</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>32936</v>
+        <v>35996</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.862155293100168</v>
+        <v>0.8591920379950997</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.743626482605768</v>
+        <v>0.7431654539465157</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.9387125783369809</v>
+        <v>0.9324022219398982</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>28748</v>
+        <v>34498</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>25157</v>
+        <v>31009</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>30754</v>
+        <v>36545</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.8978374732763762</v>
+        <v>0.9133890029665507</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.7856747997617309</v>
+        <v>0.8210180326143162</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.9605048803008421</v>
+        <v>0.9675824234289639</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>58998</v>
+        <v>67667</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>53018</v>
+        <v>62754</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>62613</v>
+        <v>71721</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.8791809619018796</v>
+        <v>0.8859935238005343</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.7900658649095402</v>
+        <v>0.8216682141574884</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.9330480354609959</v>
+        <v>0.9390756039192067</v>
       </c>
     </row>
     <row r="18">
@@ -3928,16 +3928,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>35086</v>
+        <v>38606</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>35086</v>
+        <v>38606</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>35086</v>
+        <v>38606</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -3949,16 +3949,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>32019</v>
+        <v>37769</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>32019</v>
+        <v>37769</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>32019</v>
+        <v>37769</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -3970,16 +3970,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>67106</v>
+        <v>76374</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>67106</v>
+        <v>76374</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>67106</v>
+        <v>76374</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -4003,25 +4003,25 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>12318</v>
+        <v>13368</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>7750</v>
+        <v>8642</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>18036</v>
+        <v>19368</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.2538462770261865</v>
+        <v>0.2696449441356565</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.1597165702218075</v>
+        <v>0.1743186594599799</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.3716692094072016</v>
+        <v>0.3906699947679234</v>
       </c>
       <c r="J19" s="5" t="n">
         <v>7</v>
@@ -4030,40 +4030,40 @@
         <v>4144</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>1461</v>
+        <v>1949</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>8222</v>
+        <v>8465</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0903733980401996</v>
+        <v>0.08754008075971381</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.03185582125985748</v>
+        <v>0.04117651914202325</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.1792868818028767</v>
+        <v>0.1788014232899344</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>16463</v>
+        <v>17512</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>10380</v>
+        <v>11544</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>23079</v>
+        <v>24488</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.1744193337806491</v>
+        <v>0.1806896938074185</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.1099738619578328</v>
+        <v>0.1191127290756422</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.2445153718760544</v>
+        <v>0.2526658811571016</v>
       </c>
     </row>
     <row r="20">
@@ -4080,61 +4080,61 @@
         <v>36208</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>30490</v>
+        <v>30208</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>40776</v>
+        <v>40934</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.7461537229738135</v>
+        <v>0.7303550558643435</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.6283307905927984</v>
+        <v>0.609330005232076</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.8402834297781927</v>
+        <v>0.8256813405400201</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>41715</v>
+        <v>43199</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>37637</v>
+        <v>38878</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>44398</v>
+        <v>45394</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.9096266019598004</v>
+        <v>0.9124599192402861</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.8207131181971234</v>
+        <v>0.8211985767100658</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.9681441787401426</v>
+        <v>0.9588234808579768</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>77922</v>
+        <v>79407</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>71306</v>
+        <v>72431</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>84005</v>
+        <v>85375</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.825580666219351</v>
+        <v>0.8193103061925815</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.7554846281239459</v>
+        <v>0.7473341188428978</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.8900261380421672</v>
+        <v>0.8808872709243575</v>
       </c>
     </row>
     <row r="21">
@@ -4145,16 +4145,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>48526</v>
+        <v>49576</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>48526</v>
+        <v>49576</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>48526</v>
+        <v>49576</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -4166,16 +4166,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>45859</v>
+        <v>47343</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>45859</v>
+        <v>47343</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>45859</v>
+        <v>47343</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -4187,16 +4187,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>94385</v>
+        <v>96919</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>94385</v>
+        <v>96919</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>94385</v>
+        <v>96919</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -4220,67 +4220,67 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>15468</v>
+        <v>16120</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>10295</v>
+        <v>10853</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>21996</v>
+        <v>23193</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.1462399623030922</v>
+        <v>0.1281338621610912</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.09733557589124103</v>
+        <v>0.08626884887375279</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.2079600042078818</v>
+        <v>0.1843504718980286</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>11223</v>
+        <v>13743</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>7138</v>
+        <v>9091</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>16915</v>
+        <v>20028</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1189399125590925</v>
+        <v>0.1200006514008388</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.07564616332003871</v>
+        <v>0.07938459445498369</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1792566133359111</v>
+        <v>0.174883190822641</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>26691</v>
+        <v>29863</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>19077</v>
+        <v>22109</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>35824</v>
+        <v>38859</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.1333680779881395</v>
+        <v>0.1242582580607799</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.09532381407547431</v>
+        <v>0.09199398038755642</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.1790006172420918</v>
+        <v>0.1616928959291239</v>
       </c>
     </row>
     <row r="23">
@@ -4291,67 +4291,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>90303</v>
+        <v>109688</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>83775</v>
+        <v>102615</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>95476</v>
+        <v>114955</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.8537600376969079</v>
+        <v>0.8718661378389088</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.7920399957921181</v>
+        <v>0.8156495281019716</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.902664424108759</v>
+        <v>0.9137311511262474</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>83139</v>
+        <v>100778</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>77447</v>
+        <v>94493</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>87224</v>
+        <v>105430</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.8810600874409075</v>
+        <v>0.8799993485991612</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.8207433866640886</v>
+        <v>0.825116809177359</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.9243538366799612</v>
+        <v>0.9206154055450163</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>253</v>
+        <v>308</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>173442</v>
+        <v>210466</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>164309</v>
+        <v>201470</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>181056</v>
+        <v>218220</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.8666319220118605</v>
+        <v>0.8757417419392201</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.8209993827579085</v>
+        <v>0.8383071040708755</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.9046761859245258</v>
+        <v>0.9080060196124431</v>
       </c>
     </row>
     <row r="24">
@@ -4362,16 +4362,16 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>105771</v>
+        <v>125808</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>105771</v>
+        <v>125808</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>105771</v>
+        <v>125808</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>1</v>
@@ -4383,16 +4383,16 @@
         <v>1</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>94362</v>
+        <v>114521</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>94362</v>
+        <v>114521</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>94362</v>
+        <v>114521</v>
       </c>
       <c r="N24" s="6" t="n">
         <v>1</v>
@@ -4404,16 +4404,16 @@
         <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>292</v>
+        <v>352</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>200133</v>
+        <v>240329</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>200133</v>
+        <v>240329</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>200133</v>
+        <v>240329</v>
       </c>
       <c r="U24" s="6" t="n">
         <v>1</v>
@@ -4437,67 +4437,67 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>22934</v>
+        <v>25082</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>17062</v>
+        <v>18107</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>30315</v>
+        <v>33061</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.1846581417907723</v>
+        <v>0.1722311943082714</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.1373771866993054</v>
+        <v>0.1243397185808623</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.2440928973062571</v>
+        <v>0.2270220766236936</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>17883</v>
+        <v>19294</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>12085</v>
+        <v>13730</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>24834</v>
+        <v>26672</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1523663179239034</v>
+        <v>0.1447383103348938</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.1029677576615315</v>
+        <v>0.1029961146892973</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2115912559886879</v>
+        <v>0.2000812896676857</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>40817</v>
+        <v>44376</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>32158</v>
+        <v>34793</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>51367</v>
+        <v>54930</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.1689684111608936</v>
+        <v>0.159092014518124</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.133125069865792</v>
+        <v>0.1247371280295362</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.2126430260340582</v>
+        <v>0.1969274307974091</v>
       </c>
     </row>
     <row r="26">
@@ -4508,67 +4508,67 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>101261</v>
+        <v>120546</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>93880</v>
+        <v>112567</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>107133</v>
+        <v>127521</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.8153418582092278</v>
+        <v>0.8277688056917286</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.7559071026937428</v>
+        <v>0.7729779233763063</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.8626228133006946</v>
+        <v>0.875660281419137</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>99487</v>
+        <v>114012</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>92536</v>
+        <v>106634</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>105285</v>
+        <v>119576</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.8476336820760966</v>
+        <v>0.8552616896651063</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.788408744011312</v>
+        <v>0.7999187103323149</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.8970322423384685</v>
+        <v>0.8970038853107026</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>304</v>
+        <v>357</v>
       </c>
       <c r="R26" s="5" t="n">
-        <v>200748</v>
+        <v>234557</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>190198</v>
+        <v>224003</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>209407</v>
+        <v>244140</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.8310315888391064</v>
+        <v>0.8409079854818761</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.7873569739659415</v>
+        <v>0.803072569202591</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.866874930134208</v>
+        <v>0.8752628719704639</v>
       </c>
     </row>
     <row r="27">
@@ -4579,16 +4579,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>124195</v>
+        <v>145628</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>124195</v>
+        <v>145628</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>124195</v>
+        <v>145628</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -4600,16 +4600,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>117370</v>
+        <v>133306</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>117370</v>
+        <v>133306</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>117370</v>
+        <v>133306</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -4621,16 +4621,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>368</v>
+        <v>426</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>241565</v>
+        <v>278933</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>241565</v>
+        <v>278933</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>241565</v>
+        <v>278933</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -4654,67 +4654,67 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>112567</v>
+        <v>127982</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>98079</v>
+        <v>111616</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>130076</v>
+        <v>144654</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.2147325958129284</v>
+        <v>0.2026631501550434</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.1870940664698035</v>
+        <v>0.176747335080706</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.2481324942288383</v>
+        <v>0.2290646092616782</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>67814</v>
+        <v>74064</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>57269</v>
+        <v>61213</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>82403</v>
+        <v>86772</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1391908963230728</v>
+        <v>0.128250271495198</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.1175470932371663</v>
+        <v>0.10599752830818</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1691366455307075</v>
+        <v>0.1502560382600164</v>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="R28" s="5" t="n">
-        <v>180381</v>
+        <v>202045</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>161766</v>
+        <v>181848</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>201750</v>
+        <v>224291</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.1783443098308589</v>
+        <v>0.167118795285524</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.159939460990371</v>
+        <v>0.1504129073899769</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.1994719594363856</v>
+        <v>0.1855186742623794</v>
       </c>
     </row>
     <row r="29">
@@ -4725,67 +4725,67 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>584</v>
+        <v>715</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>411654</v>
+        <v>503518</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>394145</v>
+        <v>486846</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>426142</v>
+        <v>519884</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.7852674041870716</v>
+        <v>0.7973368498449566</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.7518675057711615</v>
+        <v>0.770935390738322</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.8129059335301964</v>
+        <v>0.8232526649192942</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>622</v>
+        <v>750</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>419385</v>
+        <v>503428</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>404796</v>
+        <v>490720</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>429930</v>
+        <v>516279</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.8608091036769272</v>
+        <v>0.8717497285048019</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.8308633544692922</v>
+        <v>0.8497439617399838</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.8824529067628336</v>
+        <v>0.8940024716918201</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>1206</v>
+        <v>1465</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>831040</v>
+        <v>1006948</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>809671</v>
+        <v>984702</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>849655</v>
+        <v>1027145</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.8216556901691411</v>
+        <v>0.832881204714476</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.8005280405636144</v>
+        <v>0.8144813257376206</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.8400605390096288</v>
+        <v>0.849587092610023</v>
       </c>
     </row>
     <row r="30">
@@ -4796,16 +4796,16 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>745</v>
+        <v>897</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>1</v>
@@ -4817,16 +4817,16 @@
         <v>1</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>726</v>
+        <v>864</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="N30" s="6" t="n">
         <v>1</v>
@@ -4838,16 +4838,16 @@
         <v>1</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>1471</v>
+        <v>1761</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="U30" s="6" t="n">
         <v>1</v>
@@ -4923,7 +4923,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2023 (tasa de respuesta: 82,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5330,19 +5330,19 @@
         <v>6818</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>3104</v>
+        <v>3267</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>13740</v>
+        <v>12987</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.1627056823757861</v>
+        <v>0.1590181827395362</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.07407674869808918</v>
+        <v>0.07620982963969627</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.3278973853658317</v>
+        <v>0.3029115351852726</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>7</v>
@@ -5372,19 +5372,19 @@
         <v>12272</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>7092</v>
+        <v>6807</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>19832</v>
+        <v>20200</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.1533860963402506</v>
+        <v>0.1515456261628835</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.08864266051079366</v>
+        <v>0.08405337898825953</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.2478737955553512</v>
+        <v>0.2494446346082015</v>
       </c>
     </row>
     <row r="8">
@@ -5395,25 +5395,25 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>35084</v>
+        <v>36055</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>28162</v>
+        <v>29886</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>38798</v>
+        <v>39606</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.8372943176242138</v>
+        <v>0.8409818172604641</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.6721026146341686</v>
+        <v>0.6970884648147269</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.9259232513019108</v>
+        <v>0.9237901703603036</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>44</v>
@@ -5437,25 +5437,25 @@
         <v>0.9376761853411149</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>67736</v>
+        <v>68708</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>60176</v>
+        <v>60780</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>72916</v>
+        <v>74173</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.8466139036597492</v>
+        <v>0.8484543738371165</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.7521262044446488</v>
+        <v>0.7505553653917986</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.9113573394892065</v>
+        <v>0.9159466210117403</v>
       </c>
     </row>
     <row r="9">
@@ -5466,16 +5466,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>41902</v>
+        <v>42873</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>41902</v>
+        <v>42873</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>41902</v>
+        <v>42873</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -5508,16 +5508,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>80008</v>
+        <v>80980</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>80008</v>
+        <v>80980</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>80008</v>
+        <v>80980</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -5541,25 +5541,25 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>7209</v>
+        <v>7664</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>4214</v>
+        <v>4315</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>10745</v>
+        <v>11552</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.3300068826007778</v>
+        <v>0.3168285283778571</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.1929020757351489</v>
+        <v>0.1783640190802402</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.4918724430221533</v>
+        <v>0.4775580712521358</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>6</v>
@@ -5568,40 +5568,40 @@
         <v>3420</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1445</v>
+        <v>1310</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>6357</v>
+        <v>6318</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1598907149702696</v>
+        <v>0.151037480695843</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.06755352800685827</v>
+        <v>0.05783927472996925</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2972371833098587</v>
+        <v>0.2790318380296918</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>10629</v>
+        <v>11084</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>6562</v>
+        <v>7180</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>15304</v>
+        <v>15884</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.2458480946255779</v>
+        <v>0.2366744246560696</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.151777073180903</v>
+        <v>0.1533180529008951</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.3540023493619066</v>
+        <v>0.3391666881656266</v>
       </c>
     </row>
     <row r="11">
@@ -5612,67 +5612,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>14636</v>
+        <v>16526</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>11100</v>
+        <v>12638</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>17631</v>
+        <v>19875</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.6699931173992218</v>
+        <v>0.6831714716221428</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.508127556977847</v>
+        <v>0.5224419287478642</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.8070979242648513</v>
+        <v>0.8216359809197595</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>17967</v>
+        <v>19221</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>15030</v>
+        <v>16323</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>19942</v>
+        <v>21331</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.8401092850297304</v>
+        <v>0.8489625193041572</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.7027628166901415</v>
+        <v>0.7209681619703081</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.9324464719931417</v>
+        <v>0.9421607252700306</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>32603</v>
+        <v>35747</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>27928</v>
+        <v>30947</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>36670</v>
+        <v>39651</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.754151905374422</v>
+        <v>0.7633255753439304</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.6459976506380933</v>
+        <v>0.6608333118343733</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.8482229268190969</v>
+        <v>0.8466819470991049</v>
       </c>
     </row>
     <row r="12">
@@ -5683,37 +5683,37 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>24190</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>24190</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>24190</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="D12" s="5" t="n">
-        <v>21845</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>21845</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>21845</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>36</v>
-      </c>
       <c r="K12" s="5" t="n">
-        <v>21387</v>
+        <v>22641</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>21387</v>
+        <v>22641</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>21387</v>
+        <v>22641</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -5725,16 +5725,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>43232</v>
+        <v>46831</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>43232</v>
+        <v>46831</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>43232</v>
+        <v>46831</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -5767,16 +5767,16 @@
         <v>0</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>4914</v>
+        <v>4856</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.1127109889116028</v>
+        <v>0.08945141328850673</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.4144624618068122</v>
+        <v>0.3250250133665699</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>1</v>
@@ -5788,16 +5788,16 @@
         <v>0</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>4316</v>
+        <v>3737</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.04977940207877037</v>
+        <v>0.04845375104911621</v>
       </c>
       <c r="O13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.252759151430381</v>
+        <v>0.2130595726282877</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>3</v>
@@ -5806,19 +5806,19 @@
         <v>2186</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>5821</v>
+        <v>6256</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.07557139750553933</v>
+        <v>0.06731128119643688</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.01562801935870995</v>
+        <v>0.01330572587794042</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.2012127788458629</v>
+        <v>0.1925919836654575</v>
       </c>
     </row>
     <row r="14">
@@ -5829,67 +5829,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>10521</v>
+        <v>13605</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>6943</v>
+        <v>10085</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>11857</v>
+        <v>14941</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.8872890110883972</v>
+        <v>0.9105485867114933</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.5855375381931872</v>
+        <v>0.6749749866334301</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>16224</v>
+        <v>16691</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>12758</v>
+        <v>13804</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>17074</v>
+        <v>17541</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.9502205979212298</v>
+        <v>0.9515462489508838</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7472408485696193</v>
+        <v>0.7869404273717125</v>
       </c>
       <c r="P14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>26746</v>
+        <v>30296</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>23111</v>
+        <v>26226</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>28480</v>
+        <v>32050</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.9244286024944606</v>
+        <v>0.9326887188035632</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.7987872211541373</v>
+        <v>0.8074080163345433</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.9843719806412901</v>
+        <v>0.9866942741220597</v>
       </c>
     </row>
     <row r="15">
@@ -5900,16 +5900,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>11857</v>
+        <v>14941</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>11857</v>
+        <v>14941</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>11857</v>
+        <v>14941</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -5921,16 +5921,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>17074</v>
+        <v>17541</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>17074</v>
+        <v>17541</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>17074</v>
+        <v>17541</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -5942,16 +5942,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>28932</v>
+        <v>32482</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>28932</v>
+        <v>32482</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>28932</v>
+        <v>32482</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -5981,61 +5981,61 @@
         <v>5285</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2779</v>
+        <v>2705</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>8868</v>
+        <v>8985</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.2101792991883896</v>
+        <v>0.1973611954380402</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.1105381027095039</v>
+        <v>0.1010363289585449</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.35270852759966</v>
+        <v>0.33557021412891</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>5280</v>
+        <v>5786</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>2951</v>
+        <v>3334</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>8674</v>
+        <v>8668</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.2433352011407437</v>
+        <v>0.2542594238243148</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1360309607332048</v>
+        <v>0.1465204410228961</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.3997571099891547</v>
+        <v>0.3809338711194183</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>10564</v>
+        <v>11070</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>6822</v>
+        <v>7200</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>14511</v>
+        <v>15563</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.2255374803044445</v>
+        <v>0.2235007198928309</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.1456391785240413</v>
+        <v>0.1453627939100756</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.309807134752689</v>
+        <v>0.3141991803454234</v>
       </c>
     </row>
     <row r="17">
@@ -6046,67 +6046,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>19858</v>
+        <v>21491</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>16275</v>
+        <v>17791</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>22364</v>
+        <v>24071</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.7898207008116105</v>
+        <v>0.8026388045619597</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.6472914724003388</v>
+        <v>0.6644297858710896</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.8894618972904955</v>
+        <v>0.8989636710414536</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>16417</v>
+        <v>16969</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>13023</v>
+        <v>14087</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>18746</v>
+        <v>19421</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.7566647988592563</v>
+        <v>0.7457405761756851</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.6002428900108452</v>
+        <v>0.6190661288805817</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.8639690392667952</v>
+        <v>0.853479558977103</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>36276</v>
+        <v>38461</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>32329</v>
+        <v>33968</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>40018</v>
+        <v>42331</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.7744625196955557</v>
+        <v>0.7764992801071691</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.690192865247311</v>
+        <v>0.6858008196545767</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.8543608214759588</v>
+        <v>0.8546372060899243</v>
       </c>
     </row>
     <row r="18">
@@ -6117,16 +6117,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>25143</v>
+        <v>26776</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>25143</v>
+        <v>26776</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>25143</v>
+        <v>26776</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -6138,16 +6138,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>21697</v>
+        <v>22755</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>21697</v>
+        <v>22755</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>21697</v>
+        <v>22755</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -6159,16 +6159,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>46840</v>
+        <v>49531</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>46840</v>
+        <v>49531</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>46840</v>
+        <v>49531</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -6198,61 +6198,61 @@
         <v>5037</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>2350</v>
+        <v>2453</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>8703</v>
+        <v>8659</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.2250578501291984</v>
+        <v>0.2045955717062595</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.1049841246597333</v>
+        <v>0.0996232070448768</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.3888231557747327</v>
+        <v>0.3516748014816065</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>588</v>
+        <v>1157</v>
       </c>
       <c r="L19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>2944</v>
+        <v>3578</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.03723243253931485</v>
+        <v>0.06558415315983222</v>
       </c>
       <c r="O19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.1864239681312607</v>
+        <v>0.2027862845953532</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>5625</v>
+        <v>6195</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>2772</v>
+        <v>3194</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>9454</v>
+        <v>10329</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.1473540552280381</v>
+        <v>0.1465601664119969</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.07260054792393492</v>
+        <v>0.07557101954516675</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.2476494368768297</v>
+        <v>0.2443661582758893</v>
       </c>
     </row>
     <row r="20">
@@ -6263,67 +6263,67 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>19584</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>15962</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>22168</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0.7954044282937405</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.6483251985183935</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>0.9003767929551232</v>
+      </c>
+      <c r="J20" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D20" s="5" t="n">
-        <v>17346</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>13680</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>20033</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0.7749421498708016</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>0.6111768442252666</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>0.8950158753402667</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>24</v>
-      </c>
       <c r="K20" s="5" t="n">
-        <v>15206</v>
+        <v>16489</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>12850</v>
+        <v>14068</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>15794</v>
+        <v>17646</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.9627675674606851</v>
+        <v>0.9344158468401677</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.8135760318687394</v>
+        <v>0.797213715404646</v>
       </c>
       <c r="P20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>32551</v>
+        <v>36072</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>28722</v>
+        <v>31938</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>35404</v>
+        <v>39073</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.852645944771962</v>
+        <v>0.853439833588003</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.7523505631231702</v>
+        <v>0.755633841724111</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.9273994520760644</v>
+        <v>0.9244289804548332</v>
       </c>
     </row>
     <row r="21">
@@ -6334,16 +6334,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>22383</v>
+        <v>24621</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>22383</v>
+        <v>24621</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>22383</v>
+        <v>24621</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -6355,16 +6355,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>15794</v>
+        <v>17646</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>15794</v>
+        <v>17646</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>15794</v>
+        <v>17646</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -6376,16 +6376,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>38176</v>
+        <v>42267</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>38176</v>
+        <v>42267</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>38176</v>
+        <v>42267</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -6415,61 +6415,61 @@
         <v>19112</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>13015</v>
+        <v>13183</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>26444</v>
+        <v>26486</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.2925505081757082</v>
+        <v>0.2822043863436539</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.1992240473847112</v>
+        <v>0.1946565202261635</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.4047737442402341</v>
+        <v>0.3910799567165425</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>8554</v>
+        <v>9377</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>4893</v>
+        <v>5227</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>13984</v>
+        <v>14558</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1842662605383772</v>
+        <v>0.1887749248091128</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.1054030477528372</v>
+        <v>0.1052245641092876</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.3012383263622803</v>
+        <v>0.2930839045998028</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>27666</v>
+        <v>28489</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>19276</v>
+        <v>20879</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>35993</v>
+        <v>37536</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.2475691578578189</v>
+        <v>0.2426734141572358</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.1724855065270693</v>
+        <v>0.1778513635547236</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.3220795348448657</v>
+        <v>0.3197322971934743</v>
       </c>
     </row>
     <row r="23">
@@ -6480,67 +6480,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>46218</v>
+        <v>48613</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>38886</v>
+        <v>41239</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>52315</v>
+        <v>54542</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.7074494918242918</v>
+        <v>0.7177956136563463</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.595226255759766</v>
+        <v>0.6089200432834573</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.8007759526152888</v>
+        <v>0.8053434797738369</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>37868</v>
+        <v>40295</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>32438</v>
+        <v>35114</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>41529</v>
+        <v>44445</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.8157337394616228</v>
+        <v>0.8112250751908872</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.69876167363772</v>
+        <v>0.7069160954001973</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.8945969522471628</v>
+        <v>0.8947754358907126</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>84086</v>
+        <v>88909</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>75759</v>
+        <v>79862</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>92476</v>
+        <v>96519</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.7524308421421811</v>
+        <v>0.7573265858427641</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.6779204651551345</v>
+        <v>0.6802677028065252</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.8275144934729308</v>
+        <v>0.8221486364452761</v>
       </c>
     </row>
     <row r="24">
@@ -6551,16 +6551,16 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>65330</v>
+        <v>67725</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>65330</v>
+        <v>67725</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>65330</v>
+        <v>67725</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>1</v>
@@ -6572,16 +6572,16 @@
         <v>1</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>46422</v>
+        <v>49672</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>46422</v>
+        <v>49672</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>46422</v>
+        <v>49672</v>
       </c>
       <c r="N24" s="6" t="n">
         <v>1</v>
@@ -6593,16 +6593,16 @@
         <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>111752</v>
+        <v>117398</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>111752</v>
+        <v>117398</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>111752</v>
+        <v>117398</v>
       </c>
       <c r="U24" s="6" t="n">
         <v>1</v>
@@ -6632,19 +6632,19 @@
         <v>11296</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>6122</v>
+        <v>6368</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>17900</v>
+        <v>17326</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.1418420857842079</v>
+        <v>0.1384666229043152</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.07686892393518439</v>
+        <v>0.07806340263653903</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.2247623733226667</v>
+        <v>0.2123836151674946</v>
       </c>
       <c r="J25" s="5" t="n">
         <v>5</v>
@@ -6653,19 +6653,19 @@
         <v>2231</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>5040</v>
+        <v>4617</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.04269371870690678</v>
+        <v>0.03928013974695185</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.01581094702211937</v>
+        <v>0.01433522837356777</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.0964385069743081</v>
+        <v>0.08127689751330727</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>19</v>
@@ -6674,19 +6674,19 @@
         <v>13527</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>8577</v>
+        <v>8277</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>21389</v>
+        <v>20886</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.1025582512198531</v>
+        <v>0.09775356272138055</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.065030427562939</v>
+        <v>0.05981054236089425</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.1621591326013449</v>
+        <v>0.1509272279698203</v>
       </c>
     </row>
     <row r="26">
@@ -6697,67 +6697,67 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>68343</v>
+        <v>70284</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>61739</v>
+        <v>64254</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>73517</v>
+        <v>75212</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.8581579142157921</v>
+        <v>0.8615333770956849</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.7752376266773335</v>
+        <v>0.7876163848325048</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.923131076064816</v>
+        <v>0.9219365973634608</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>50029</v>
+        <v>54571</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>47220</v>
+        <v>52185</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>51434</v>
+        <v>55988</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.9573062812930933</v>
+        <v>0.9607198602530481</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.9035614930256919</v>
+        <v>0.9187231024866926</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.9841890529778805</v>
+        <v>0.9856647716264323</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="R26" s="5" t="n">
-        <v>118372</v>
+        <v>124855</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>110510</v>
+        <v>117496</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>123322</v>
+        <v>130105</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.897441748780147</v>
+        <v>0.9022464372786194</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.8378408673986553</v>
+        <v>0.8490727720301801</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.934969572437061</v>
+        <v>0.940189457639106</v>
       </c>
     </row>
     <row r="27">
@@ -6768,16 +6768,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>79639</v>
+        <v>81580</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>79639</v>
+        <v>81580</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>79639</v>
+        <v>81580</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -6789,16 +6789,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>52260</v>
+        <v>56802</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>52260</v>
+        <v>56802</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>52260</v>
+        <v>56802</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -6810,16 +6810,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>131899</v>
+        <v>138382</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>131899</v>
+        <v>138382</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>131899</v>
+        <v>138382</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -6843,67 +6843,67 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>58938</v>
+        <v>59393</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>47575</v>
+        <v>48288</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>73107</v>
+        <v>73321</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.199577453218781</v>
+        <v>0.1916390354652999</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.1610977255455545</v>
+        <v>0.1558067116395825</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.2475552608383892</v>
+        <v>0.2365777460481445</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>27638</v>
+        <v>29537</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>20735</v>
+        <v>22057</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>36256</v>
+        <v>38734</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1170031953429169</v>
+        <v>0.1187915259234743</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.0877790334129884</v>
+        <v>0.08870829937120299</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.153483405076763</v>
+        <v>0.1557822107223183</v>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="R28" s="5" t="n">
-        <v>86577</v>
+        <v>88930</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>74318</v>
+        <v>76113</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>104601</v>
+        <v>105663</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.16288063728964</v>
+        <v>0.1592113937317494</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.1398170843121347</v>
+        <v>0.136264711853671</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.1967909768119987</v>
+        <v>0.1891680988468435</v>
       </c>
     </row>
     <row r="29">
@@ -6914,67 +6914,67 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>236377</v>
+        <v>250530</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>222208</v>
+        <v>236602</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>247740</v>
+        <v>261635</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.8004225467812189</v>
+        <v>0.8083609645347002</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.7524447391616108</v>
+        <v>0.7634222539518554</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.8389022744544455</v>
+        <v>0.8441932883604175</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>208581</v>
+        <v>219105</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>199963</v>
+        <v>209908</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>215484</v>
+        <v>226585</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.8829968046570831</v>
+        <v>0.8812084740765257</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.8465165949232369</v>
+        <v>0.8442177892776818</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.9122209665870115</v>
+        <v>0.9112917006287971</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>632</v>
+        <v>667</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>444957</v>
+        <v>469635</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>426933</v>
+        <v>452902</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>457216</v>
+        <v>482452</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.83711936271036</v>
+        <v>0.8407886062682505</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.8032090231880011</v>
+        <v>0.8108319011531568</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.8601829156878655</v>
+        <v>0.8637352881463292</v>
       </c>
     </row>
     <row r="30">
@@ -6985,16 +6985,16 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>1</v>
@@ -7006,16 +7006,16 @@
         <v>1</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="N30" s="6" t="n">
         <v>1</v>
@@ -7027,16 +7027,16 @@
         <v>1</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>766</v>
+        <v>805</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="U30" s="6" t="n">
         <v>1</v>
